--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/guild_master_merchant.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/guild_master_merchant.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr autoCompressPictures="1"/>
-  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="1" sheetId="1" r:id="rId2"/>
+    <sheet name="1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
-    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -184,45 +184,6 @@
   </si>
   <si>
     <t xml:space="preserve">reload</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">传单发得怎么样了？你不是在偷懒吧？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哦呀哦呀，有什么事？我在忙着呢。说简短点。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我想加入商人公会</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哦呀哦呀，想加入商人公会？
-只要在经营生意，谁都可以无条件加入商人公会，真正的生意人都知道这件事。
-你真的是生意人吗？怎么穿着像冒险者一样肮脏的衣服？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哼，真有趣。我还挺喜欢你那个反抗的态度。我玛丽安女士就给你安排一场考试吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">嗯…作为入团考试就让你发传单吧。从接待员小姐那里大量购买传单，再去某个城市分发就好。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">送给初出茅庐的你一个建议吧。
-听好了，发传单这件事可不能小心翼翼的给别人递过去。而是要站在人群的中心发挥热情，见人就给他们塞过去。
-好了，冲到街上，去展现你的商人之魂吧！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哦呀哦呀，传单发完了吗？看来你想做生意的干劲是真格的。
-好吧，欢迎你加入商人公会。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你怎么一脸如释重负的表情？可别因为进了公会就得意忘形啊。
-你现在踏入的世界，是恶魔们的战场。在这里，连灵魂的重量都要用金钱来衡量。如果疏忽大意的话，马上就会被吃干抹净。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…呵呵。不过你也不用担心。你可是玛丽安女士看中的商人。我期待着你的名字能让商业巨头们都为之胆颤的那一天。</t>
   </si>
 </sst>
 </file>
@@ -244,32 +205,32 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -288,7 +249,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -297,58 +258,58 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
-      <alignment/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -362,13 +323,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <family val="2"/>
         <color rgb="FFCC0000"/>
-        <name val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -438,25 +399,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L37"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="2" width="8.85" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.56" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.2" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.85" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.12" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85" style="1" customWidth="1"/>
-    <col min="8" max="9" width="7.09" style="1" customWidth="1"/>
-    <col min="10" max="10" width="42.14" style="1" customWidth="1"/>
-    <col min="11" max="11" width="53.28" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="7.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="42.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="53.28"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -494,30 +455,30 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="12.8">
-      <c r="I2" s="1">
-        <f>MAX(I4:I1048576)</f>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I2" s="1" t="n">
+        <f aca="false">MAX(I4:I1048576)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="6" ht="12.8">
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" ht="12.8">
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" ht="12.8">
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D10" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I10" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="1" t="s">
@@ -526,11 +487,8 @@
       <c r="K10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="L10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" ht="12.8">
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
         <v>18</v>
       </c>
@@ -538,19 +496,19 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" ht="12.8">
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D12" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" ht="12.8">
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D13" s="3"/>
     </row>
-    <row r="14" ht="12.8">
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D14" s="3"/>
     </row>
-    <row r="15" ht="12.8">
-      <c r="I15" s="1">
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I15" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J15" s="1" t="s">
@@ -559,11 +517,8 @@
       <c r="K15" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" ht="12.8">
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="1" t="s">
         <v>23</v>
       </c>
@@ -573,7 +528,7 @@
       <c r="E16" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I16" s="1">
+      <c r="I16" s="1" t="n">
         <v>2</v>
       </c>
       <c r="J16" s="1" t="s">
@@ -582,11 +537,8 @@
       <c r="K16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L16" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" ht="12.8">
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E17" s="1" t="s">
         <v>28</v>
       </c>
@@ -594,23 +546,23 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" ht="12.8">
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E18" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="19" ht="12.8">
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E19" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="22" ht="12.8">
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="23" ht="91">
-      <c r="I23" s="1">
+    <row r="23" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J23" s="4" t="s">
@@ -619,12 +571,9 @@
       <c r="K23" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="L23" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" ht="35.05">
-      <c r="I24" s="1">
+    </row>
+    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I24" s="1" t="n">
         <v>4</v>
       </c>
       <c r="J24" s="4" t="s">
@@ -633,12 +582,9 @@
       <c r="K24" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="L24" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" ht="46.25">
-      <c r="I25" s="1">
+    </row>
+    <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I25" s="1" t="n">
         <v>5</v>
       </c>
       <c r="J25" s="4" t="s">
@@ -647,11 +593,8 @@
       <c r="K25" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="L25" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" ht="12.8">
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D26" s="3"/>
       <c r="E26" s="1" t="s">
         <v>38</v>
@@ -660,9 +603,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="27" ht="102.2">
+    <row r="27" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D27" s="3"/>
-      <c r="I27" s="1">
+      <c r="I27" s="1" t="n">
         <v>6</v>
       </c>
       <c r="J27" s="4" t="s">
@@ -671,26 +614,23 @@
       <c r="K27" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="L27" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="28" ht="12.8">
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" ht="12.8">
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D29" s="3"/>
     </row>
-    <row r="31" ht="12.8">
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="32" ht="68.65">
-      <c r="I32" s="1">
+    <row r="32" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I32" s="1" t="n">
         <v>7</v>
       </c>
       <c r="J32" s="6" t="s">
@@ -699,11 +639,8 @@
       <c r="K32" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="L32" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="33" ht="12.8">
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D33" s="3"/>
       <c r="E33" s="1" t="s">
         <v>38</v>
@@ -712,8 +649,8 @@
         <v>45</v>
       </c>
     </row>
-    <row r="34" ht="68.65">
-      <c r="I34" s="1">
+    <row r="34" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I34" s="1" t="n">
         <v>8</v>
       </c>
       <c r="J34" s="4" t="s">
@@ -722,12 +659,9 @@
       <c r="K34" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="L34" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="35" ht="46.25">
-      <c r="I35" s="1">
+    </row>
+    <row r="35" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I35" s="1" t="n">
         <v>9</v>
       </c>
       <c r="J35" s="4" t="s">
@@ -736,28 +670,25 @@
       <c r="K35" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="L35" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="36" ht="12.8">
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E36" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="37" ht="12.8">
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="1" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I4:I1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/guild_master_merchant.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/guild_master_merchant.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+  <workbookPr autoCompressPictures="1"/>
+  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="1" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="62">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -184,6 +184,45 @@
   </si>
   <si>
     <t xml:space="preserve">reload</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">传单发得怎么样了？你不是在偷懒吧？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哦呀哦呀，有什么事？我在忙着呢。说简短点。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我想加入商人公会</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哦呀哦呀，想加入商人公会？
+只要在经营生意，谁都可以无条件加入商人公会，真正的生意人都知道这件事。
+你真的是生意人吗？怎么穿着像冒险者一样肮脏的衣服？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哼，真有趣。我还挺喜欢你那个反抗的态度。我玛丽安女士就给你安排一场考试吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嗯…作为入团考试就让你发传单吧。从接待员小姐那里大量购买传单，再去某个城市分发就好。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">送给初出茅庐的你一个建议吧。
+听好了，发传单这件事可不能小心翼翼的给别人递过去。而是要站在人群的中心发挥热情，见人就给他们塞过去。
+好了，冲到街上，去展现你的商人之魂吧！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哦呀哦呀，传单发完了吗？看来你想做生意的干劲是真格的。
+好吧，欢迎你加入商人公会。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你怎么一脸如释重负的表情？可别因为进了公会就得意忘形啊。
+你现在踏入的世界，是恶魔们的战场。在这里，连灵魂的重量都要用金钱来衡量。如果疏忽大意的话，马上就会被吃干抹净。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…呵呵。不过你也不用担心。你可是玛丽安女士看中的商人。我期待着你的名字能让商业巨头们都为之胆颤的那一天。</t>
   </si>
 </sst>
 </file>
@@ -205,32 +244,32 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -249,7 +288,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -258,58 +297,58 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -323,13 +362,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <color rgb="FFCC0000"/>
         <name val="游ゴシック"/>
+        <family val="2"/>
         <charset val="128"/>
-        <family val="2"/>
-        <color rgb="FFCC0000"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -399,25 +438,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L37"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="7.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="42.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="53.28"/>
+    <col min="1" max="2" width="8.85" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.56" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.2" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.12" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85" style="1" customWidth="1"/>
+    <col min="8" max="9" width="7.09" style="1" customWidth="1"/>
+    <col min="10" max="10" width="42.14" style="1" customWidth="1"/>
+    <col min="11" max="11" width="53.28" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -455,30 +494,30 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I2" s="1" t="n">
-        <f aca="false">MAX(I4:I1048576)</f>
+    <row r="2" ht="12.8">
+      <c r="I2" s="1">
+        <f>MAX(I4:I1048576)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" ht="12.8">
       <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" ht="12.8">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" ht="12.8">
       <c r="D10" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I10" s="1" t="n">
+      <c r="I10" s="1">
         <v>0</v>
       </c>
       <c r="J10" s="1" t="s">
@@ -487,8 +526,11 @@
       <c r="K10" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" ht="12.8">
       <c r="B11" s="1" t="s">
         <v>18</v>
       </c>
@@ -496,19 +538,19 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" ht="12.8">
       <c r="D12" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" ht="12.8">
       <c r="D13" s="3"/>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" ht="12.8">
       <c r="D14" s="3"/>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I15" s="1" t="n">
+    <row r="15" ht="12.8">
+      <c r="I15" s="1">
         <v>1</v>
       </c>
       <c r="J15" s="1" t="s">
@@ -517,8 +559,11 @@
       <c r="K15" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" ht="12.8">
       <c r="B16" s="1" t="s">
         <v>23</v>
       </c>
@@ -528,7 +573,7 @@
       <c r="E16" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I16" s="1" t="n">
+      <c r="I16" s="1">
         <v>2</v>
       </c>
       <c r="J16" s="1" t="s">
@@ -537,8 +582,11 @@
       <c r="K16" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" ht="12.8">
       <c r="E17" s="1" t="s">
         <v>28</v>
       </c>
@@ -546,23 +594,23 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" ht="12.8">
       <c r="E18" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" ht="12.8">
       <c r="E19" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" ht="12.8">
       <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I23" s="1" t="n">
+    <row r="23" ht="91">
+      <c r="I23" s="1">
         <v>3</v>
       </c>
       <c r="J23" s="4" t="s">
@@ -571,9 +619,12 @@
       <c r="K23" s="5" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I24" s="1" t="n">
+      <c r="L23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" ht="35.05">
+      <c r="I24" s="1">
         <v>4</v>
       </c>
       <c r="J24" s="4" t="s">
@@ -582,9 +633,12 @@
       <c r="K24" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I25" s="1" t="n">
+      <c r="L24" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" ht="46.25">
+      <c r="I25" s="1">
         <v>5</v>
       </c>
       <c r="J25" s="4" t="s">
@@ -593,8 +647,11 @@
       <c r="K25" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L25" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" ht="12.8">
       <c r="D26" s="3"/>
       <c r="E26" s="1" t="s">
         <v>38</v>
@@ -603,9 +660,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" ht="102.2">
       <c r="D27" s="3"/>
-      <c r="I27" s="1" t="n">
+      <c r="I27" s="1">
         <v>6</v>
       </c>
       <c r="J27" s="4" t="s">
@@ -614,23 +671,26 @@
       <c r="K27" s="5" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" ht="12.8">
       <c r="B28" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" ht="12.8">
       <c r="D29" s="3"/>
     </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" ht="12.8">
       <c r="A31" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I32" s="1" t="n">
+    <row r="32" ht="68.65">
+      <c r="I32" s="1">
         <v>7</v>
       </c>
       <c r="J32" s="6" t="s">
@@ -639,8 +699,11 @@
       <c r="K32" s="5" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L32" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" ht="12.8">
       <c r="D33" s="3"/>
       <c r="E33" s="1" t="s">
         <v>38</v>
@@ -649,8 +712,8 @@
         <v>45</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I34" s="1" t="n">
+    <row r="34" ht="68.65">
+      <c r="I34" s="1">
         <v>8</v>
       </c>
       <c r="J34" s="4" t="s">
@@ -659,9 +722,12 @@
       <c r="K34" s="5" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I35" s="1" t="n">
+      <c r="L34" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" ht="46.25">
+      <c r="I35" s="1">
         <v>9</v>
       </c>
       <c r="J35" s="4" t="s">
@@ -670,25 +736,28 @@
       <c r="K35" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L35" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" ht="12.8">
       <c r="E36" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" ht="12.8">
       <c r="B37" s="1" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I4:I1048576">
-    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
